--- a/ui_runner/graded_slate/2026-04-02/graded_cbb_2026-04-02.xlsx
+++ b/ui_runner/graded_slate/2026-04-02/graded_cbb_2026-04-02.xlsx
@@ -695,7 +695,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CBB SLATE GRADE  |  2026-04-02  |  Generated 2026-04-03 15:38</t>
+          <t>CBB SLATE GRADE  |  2026-04-02  |  Generated 2026-04-03 18:59</t>
         </is>
       </c>
     </row>

--- a/ui_runner/graded_slate/2026-04-02/graded_cbb_2026-04-02.xlsx
+++ b/ui_runner/graded_slate/2026-04-02/graded_cbb_2026-04-02.xlsx
@@ -62,7 +62,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -106,12 +106,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6EAF8"/>
+        <fgColor rgb="00E74C3C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E74C3C"/>
+        <fgColor rgb="00D6EAF8"/>
       </patternFill>
     </fill>
     <fill>
@@ -146,22 +146,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDDDDD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00922B21"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="006C3483"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0095A5A6"/>
       </patternFill>
     </fill>
   </fills>
@@ -191,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -223,13 +213,13 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -262,13 +252,10 @@
     <xf numFmtId="0" fontId="4" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -283,10 +270,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -301,7 +285,7 @@
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -695,7 +679,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CBB SLATE GRADE  |  2026-04-02  |  Generated 2026-04-03 18:59</t>
+          <t>CBB SLATE GRADE  |  2026-04-02  |  Generated 2026-04-13 21:14</t>
         </is>
       </c>
     </row>
@@ -756,19 +740,19 @@
         <v>117</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>53</v>
+        <v>117</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>0.5849056603773585</v>
+        <v>0.5384615384615384</v>
       </c>
     </row>
     <row r="5">
@@ -828,19 +812,19 @@
         <v>57</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.6470588235294118</v>
+        <v>0.631578947368421</v>
       </c>
     </row>
     <row r="7">
@@ -858,45 +842,45 @@
         <v>60</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>0.5555555555555556</v>
+        <v>0</v>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>0.45</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr"/>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr"/>
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="D8" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="11" t="n">
+      <c r="D8" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="E8" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="G8" s="11" t="n">
-        <v>24</v>
-      </c>
-      <c r="H8" s="13" t="n">
-        <v>0.1111111111111111</v>
+      <c r="F8" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="11" t="n">
+        <v>0.2424242424242424</v>
       </c>
     </row>
     <row r="9">
@@ -998,25 +982,25 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr"/>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="C13" s="11" t="n">
+      <c r="C13" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="F13" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G13" s="11" t="n">
+      <c r="G13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="5" t="n">
@@ -1055,54 +1039,54 @@
           <t>Tier B</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="C15" s="11" t="n">
+      <c r="C15" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="E15" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="F15" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="16" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr"/>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="E16" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="F15" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" s="11" t="n">
+      <c r="F16" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H15" s="16" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr"/>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="D16" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="E16" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="F16" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="G16" s="11" t="n">
-        <v>5</v>
+      <c r="G16" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="17">
@@ -1146,45 +1130,45 @@
         <v>33</v>
       </c>
       <c r="D18" s="21" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0.5625</v>
+        <v>0.6060606060606061</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr"/>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr"/>
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="C19" s="11" t="n">
+      <c r="C19" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="E19" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G19" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="H19" s="13" t="n">
-        <v>0.125</v>
+      <c r="D19" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="11" t="n">
+        <v>0.48</v>
       </c>
     </row>
     <row r="20">
@@ -1228,44 +1212,46 @@
         <v>50</v>
       </c>
       <c r="D21" s="23" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="E21" s="23" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F21" s="23" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="G21" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="11" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr"/>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="H21" s="5" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr"/>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="n">
+      <c r="D22" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="D22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="11" t="n">
-        <v>42</v>
-      </c>
-      <c r="H22" s="24" t="inlineStr"/>
+      <c r="E22" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="11" t="n">
+        <v>0.4285714285714285</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr"/>
@@ -1294,84 +1280,84 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="24" t="inlineStr">
         <is>
           <t>BY OPP DEF TIER</t>
         </is>
       </c>
-      <c r="B25" s="25" t="inlineStr">
+      <c r="B25" s="24" t="inlineStr">
         <is>
           <t>Direction</t>
         </is>
       </c>
-      <c r="C25" s="25" t="inlineStr">
+      <c r="C25" s="24" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="D25" s="25" t="inlineStr">
+      <c r="D25" s="24" t="inlineStr">
         <is>
           <t>Decided</t>
         </is>
       </c>
-      <c r="E25" s="25" t="inlineStr">
+      <c r="E25" s="24" t="inlineStr">
         <is>
           <t>Hits</t>
         </is>
       </c>
-      <c r="F25" s="25" t="inlineStr">
+      <c r="F25" s="24" t="inlineStr">
         <is>
           <t>Misses</t>
         </is>
       </c>
-      <c r="G25" s="25" t="inlineStr">
+      <c r="G25" s="24" t="inlineStr">
         <is>
           <t>Voids</t>
         </is>
       </c>
-      <c r="H25" s="25" t="inlineStr">
+      <c r="H25" s="24" t="inlineStr">
         <is>
           <t>Hit Rate</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="25" t="inlineStr">
+      <c r="A27" s="24" t="inlineStr">
         <is>
           <t>BY OPP DEF RANK BUCKET</t>
         </is>
       </c>
-      <c r="B27" s="25" t="inlineStr">
+      <c r="B27" s="24" t="inlineStr">
         <is>
           <t>Direction</t>
         </is>
       </c>
-      <c r="C27" s="25" t="inlineStr">
+      <c r="C27" s="24" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="D27" s="25" t="inlineStr">
+      <c r="D27" s="24" t="inlineStr">
         <is>
           <t>Decided</t>
         </is>
       </c>
-      <c r="E27" s="25" t="inlineStr">
+      <c r="E27" s="24" t="inlineStr">
         <is>
           <t>Hits</t>
         </is>
       </c>
-      <c r="F27" s="25" t="inlineStr">
+      <c r="F27" s="24" t="inlineStr">
         <is>
           <t>Misses</t>
         </is>
       </c>
-      <c r="G27" s="25" t="inlineStr">
+      <c r="G27" s="24" t="inlineStr">
         <is>
           <t>Voids</t>
         </is>
       </c>
-      <c r="H27" s="25" t="inlineStr">
+      <c r="H27" s="24" t="inlineStr">
         <is>
           <t>Hit Rate</t>
         </is>
@@ -1392,45 +1378,45 @@
         <v>117</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>53</v>
+        <v>117</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>0.5849056603773585</v>
+        <v>0.5384615384615384</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="inlineStr"/>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="A29" s="12" t="inlineStr"/>
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="C29" s="11" t="n">
+      <c r="C29" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="D29" s="11" t="n">
-        <v>26</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="F29" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="G29" s="11" t="n">
-        <v>64</v>
-      </c>
-      <c r="H29" s="13" t="n">
-        <v>0.4615384615384616</v>
+      <c r="D29" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="11" t="n">
+        <v>0.4888888888888889</v>
       </c>
     </row>
     <row r="30">
@@ -1460,42 +1446,42 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="26" t="inlineStr">
+      <c r="A32" s="25" t="inlineStr">
         <is>
           <t>BY MINUTES TIER</t>
         </is>
       </c>
-      <c r="B32" s="26" t="inlineStr">
+      <c r="B32" s="25" t="inlineStr">
         <is>
           <t>Direction</t>
         </is>
       </c>
-      <c r="C32" s="26" t="inlineStr">
+      <c r="C32" s="25" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="D32" s="26" t="inlineStr">
+      <c r="D32" s="25" t="inlineStr">
         <is>
           <t>Decided</t>
         </is>
       </c>
-      <c r="E32" s="26" t="inlineStr">
+      <c r="E32" s="25" t="inlineStr">
         <is>
           <t>Hits</t>
         </is>
       </c>
-      <c r="F32" s="26" t="inlineStr">
+      <c r="F32" s="25" t="inlineStr">
         <is>
           <t>Misses</t>
         </is>
       </c>
-      <c r="G32" s="26" t="inlineStr">
+      <c r="G32" s="25" t="inlineStr">
         <is>
           <t>Voids</t>
         </is>
       </c>
-      <c r="H32" s="26" t="inlineStr">
+      <c r="H32" s="25" t="inlineStr">
         <is>
           <t>Hit Rate</t>
         </is>
@@ -1528,44 +1514,44 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="27" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>void_reason</t>
         </is>
       </c>
-      <c r="B1" s="27" t="inlineStr">
+      <c r="B1" s="26" t="inlineStr">
         <is>
           <t>total</t>
         </is>
       </c>
-      <c r="C1" s="27" t="inlineStr">
+      <c r="C1" s="26" t="inlineStr">
         <is>
           <t>hit</t>
         </is>
       </c>
-      <c r="D1" s="27" t="inlineStr">
+      <c r="D1" s="26" t="inlineStr">
         <is>
           <t>miss</t>
         </is>
       </c>
-      <c r="E1" s="27" t="inlineStr">
+      <c r="E1" s="26" t="inlineStr">
         <is>
           <t>void</t>
         </is>
       </c>
-      <c r="F1" s="27" t="inlineStr">
+      <c r="F1" s="26" t="inlineStr">
         <is>
           <t>decided</t>
         </is>
       </c>
-      <c r="G1" s="27" t="inlineStr">
+      <c r="G1" s="26" t="inlineStr">
         <is>
           <t>hit_rate</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="28" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
         </is>
@@ -1574,21 +1560,23 @@
         <v>31</v>
       </c>
       <c r="C2" s="10" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="F2" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="24" t="inlineStr"/>
+      <c r="G2" s="11" t="n">
+        <v>0.4516</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="29" t="inlineStr">
         <is>
           <t>VOID_LOW_MINUTES_NON_A</t>
         </is>
@@ -1597,21 +1585,23 @@
         <v>22</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="F3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="24" t="inlineStr"/>
+      <c r="G3" s="5" t="n">
+        <v>0.6364</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>VOID_TIER_D</t>
         </is>
@@ -1620,18 +1610,20 @@
         <v>11</v>
       </c>
       <c r="C4" s="10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="F4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="24" t="inlineStr"/>
+      <c r="G4" s="11" t="n">
+        <v>0.3636</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1670,109 +1662,109 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="27" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="27" t="inlineStr">
+      <c r="B1" s="26" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="C1" s="27" t="inlineStr">
+      <c r="C1" s="26" t="inlineStr">
         <is>
           <t>opp_team</t>
         </is>
       </c>
-      <c r="D1" s="27" t="inlineStr">
+      <c r="D1" s="26" t="inlineStr">
         <is>
           <t>prop_type_norm</t>
         </is>
       </c>
-      <c r="E1" s="27" t="inlineStr">
+      <c r="E1" s="26" t="inlineStr">
         <is>
           <t>pick_type</t>
         </is>
       </c>
-      <c r="F1" s="27" t="inlineStr">
+      <c r="F1" s="26" t="inlineStr">
         <is>
           <t>line</t>
         </is>
       </c>
-      <c r="G1" s="27" t="inlineStr">
+      <c r="G1" s="26" t="inlineStr">
         <is>
           <t>bet_direction</t>
         </is>
       </c>
-      <c r="H1" s="27" t="inlineStr">
+      <c r="H1" s="26" t="inlineStr">
         <is>
           <t>tier</t>
         </is>
       </c>
-      <c r="I1" s="27" t="inlineStr">
+      <c r="I1" s="26" t="inlineStr">
         <is>
           <t>def_tier</t>
         </is>
       </c>
-      <c r="J1" s="27" t="inlineStr">
+      <c r="J1" s="26" t="inlineStr">
         <is>
           <t>minutes_tier</t>
         </is>
       </c>
-      <c r="K1" s="27" t="inlineStr">
+      <c r="K1" s="26" t="inlineStr">
         <is>
           <t>edge</t>
         </is>
       </c>
-      <c r="L1" s="27" t="inlineStr">
+      <c r="L1" s="26" t="inlineStr">
         <is>
           <t>abs_edge</t>
         </is>
       </c>
-      <c r="M1" s="27" t="inlineStr">
+      <c r="M1" s="26" t="inlineStr">
         <is>
           <t>projection</t>
         </is>
       </c>
-      <c r="N1" s="27" t="inlineStr">
+      <c r="N1" s="26" t="inlineStr">
         <is>
           <t>rank_score</t>
         </is>
       </c>
-      <c r="O1" s="27" t="inlineStr">
+      <c r="O1" s="26" t="inlineStr">
         <is>
           <t>ml_prob</t>
         </is>
       </c>
-      <c r="P1" s="27" t="inlineStr">
+      <c r="P1" s="26" t="inlineStr">
         <is>
           <t>ml_edge</t>
         </is>
       </c>
-      <c r="Q1" s="27" t="inlineStr">
+      <c r="Q1" s="26" t="inlineStr">
         <is>
           <t>actual</t>
         </is>
       </c>
-      <c r="R1" s="27" t="inlineStr">
+      <c r="R1" s="26" t="inlineStr">
         <is>
           <t>result</t>
         </is>
       </c>
-      <c r="S1" s="27" t="inlineStr">
+      <c r="S1" s="26" t="inlineStr">
         <is>
           <t>margin</t>
         </is>
       </c>
-      <c r="T1" s="27" t="inlineStr">
+      <c r="T1" s="26" t="inlineStr">
         <is>
           <t>void_reason_grade</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="28" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>Chase Walker</t>
         </is>
@@ -1839,7 +1831,7 @@
       <c r="Q2" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="R2" s="29" t="inlineStr">
+      <c r="R2" s="28" t="inlineStr">
         <is>
           <t>HIT</t>
         </is>
@@ -1847,12 +1839,10 @@
       <c r="S2" s="10" t="n">
         <v>3.5</v>
       </c>
-      <c r="T2" s="10" t="n">
-        <v/>
-      </c>
+      <c r="T2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="29" t="inlineStr">
         <is>
           <t>Johnny Kinziger</t>
         </is>
@@ -1919,7 +1909,7 @@
       <c r="Q3" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="R3" s="31" t="inlineStr">
+      <c r="R3" s="30" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
@@ -1927,12 +1917,10 @@
       <c r="S3" s="4" t="n">
         <v>-4.5</v>
       </c>
-      <c r="T3" s="4" t="n">
-        <v/>
-      </c>
+      <c r="T3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>Brenen Lorient</t>
         </is>
@@ -1999,7 +1987,7 @@
       <c r="Q4" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="R4" s="29" t="inlineStr">
+      <c r="R4" s="28" t="inlineStr">
         <is>
           <t>HIT</t>
         </is>
@@ -2007,12 +1995,10 @@
       <c r="S4" s="10" t="n">
         <v>4.5</v>
       </c>
-      <c r="T4" s="10" t="n">
-        <v/>
-      </c>
+      <c r="T4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>Keyshawn Hall</t>
         </is>
@@ -2079,7 +2065,7 @@
       <c r="Q5" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="R5" s="31" t="inlineStr">
+      <c r="R5" s="30" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
@@ -2087,12 +2073,10 @@
       <c r="S5" s="4" t="n">
         <v>-2.5</v>
       </c>
-      <c r="T5" s="4" t="n">
-        <v/>
-      </c>
+      <c r="T5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Tylen Riley</t>
         </is>
@@ -2159,7 +2143,7 @@
       <c r="Q6" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="R6" s="29" t="inlineStr">
+      <c r="R6" s="28" t="inlineStr">
         <is>
           <t>HIT</t>
         </is>
@@ -2167,12 +2151,10 @@
       <c r="S6" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="T6" s="10" t="n">
-        <v/>
-      </c>
+      <c r="T6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>Keyshawn Hall</t>
         </is>
@@ -2239,7 +2221,7 @@
       <c r="Q7" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="R7" s="31" t="inlineStr">
+      <c r="R7" s="30" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
@@ -2247,12 +2229,10 @@
       <c r="S7" s="4" t="n">
         <v>-3.5</v>
       </c>
-      <c r="T7" s="4" t="n">
-        <v/>
-      </c>
+      <c r="T7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="28" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>Keyshawn Hall</t>
         </is>
@@ -2319,7 +2299,7 @@
       <c r="Q8" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="R8" s="31" t="inlineStr">
+      <c r="R8" s="30" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
@@ -2327,12 +2307,10 @@
       <c r="S8" s="10" t="n">
         <v>-4.5</v>
       </c>
-      <c r="T8" s="10" t="n">
-        <v/>
-      </c>
+      <c r="T8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="inlineStr">
+      <c r="A9" s="29" t="inlineStr">
         <is>
           <t>Johnny Kinziger</t>
         </is>
@@ -2399,7 +2377,7 @@
       <c r="Q9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="R9" s="29" t="inlineStr">
+      <c r="R9" s="28" t="inlineStr">
         <is>
           <t>HIT</t>
         </is>
@@ -2407,12 +2385,10 @@
       <c r="S9" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="T9" s="4" t="n">
-        <v/>
-      </c>
+      <c r="T9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="28" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>Tomislav Buljan</t>
         </is>
@@ -2479,7 +2455,7 @@
       <c r="Q10" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="R10" s="31" t="inlineStr">
+      <c r="R10" s="30" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
@@ -2487,12 +2463,10 @@
       <c r="S10" s="10" t="n">
         <v>-2.5</v>
       </c>
-      <c r="T10" s="10" t="n">
-        <v/>
-      </c>
+      <c r="T10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="inlineStr">
+      <c r="A11" s="29" t="inlineStr">
         <is>
           <t>Tomislav Buljan</t>
         </is>
@@ -2559,7 +2533,7 @@
       <c r="Q11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="31" t="inlineStr">
+      <c r="R11" s="30" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
@@ -2567,12 +2541,10 @@
       <c r="S11" s="4" t="n">
         <v>-1.5</v>
       </c>
-      <c r="T11" s="4" t="n">
-        <v/>
-      </c>
+      <c r="T11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>Keyshawn Hall</t>
         </is>
@@ -2639,7 +2611,7 @@
       <c r="Q12" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="R12" s="31" t="inlineStr">
+      <c r="R12" s="30" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
@@ -2647,12 +2619,10 @@
       <c r="S12" s="10" t="n">
         <v>-5.5</v>
       </c>
-      <c r="T12" s="10" t="n">
-        <v/>
-      </c>
+      <c r="T12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="30" t="inlineStr">
+      <c r="A13" s="29" t="inlineStr">
         <is>
           <t>Ade Popoola</t>
         </is>
@@ -2719,7 +2689,7 @@
       <c r="Q13" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="R13" s="29" t="inlineStr">
+      <c r="R13" s="28" t="inlineStr">
         <is>
           <t>HIT</t>
         </is>
@@ -2727,12 +2697,10 @@
       <c r="S13" s="4" t="n">
         <v>2.5</v>
       </c>
-      <c r="T13" s="4" t="n">
-        <v/>
-      </c>
+      <c r="T13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="28" t="inlineStr">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>Kevin Overton</t>
         </is>
@@ -2799,7 +2767,7 @@
       <c r="Q14" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="R14" s="29" t="inlineStr">
+      <c r="R14" s="28" t="inlineStr">
         <is>
           <t>HIT</t>
         </is>
@@ -2807,12 +2775,10 @@
       <c r="S14" s="10" t="n">
         <v>6.5</v>
       </c>
-      <c r="T14" s="10" t="n">
-        <v/>
-      </c>
+      <c r="T14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="30" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>Tahaad Pettiford</t>
         </is>
@@ -2879,7 +2845,7 @@
       <c r="Q15" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="R15" s="29" t="inlineStr">
+      <c r="R15" s="28" t="inlineStr">
         <is>
           <t>HIT</t>
         </is>
@@ -2887,12 +2853,10 @@
       <c r="S15" s="4" t="n">
         <v>6.5</v>
       </c>
-      <c r="T15" s="4" t="n">
-        <v/>
-      </c>
+      <c r="T15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="28" t="inlineStr">
+      <c r="A16" s="27" t="inlineStr">
         <is>
           <t>Elyjah Freeman</t>
         </is>
@@ -2959,7 +2923,7 @@
       <c r="Q16" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="R16" s="29" t="inlineStr">
+      <c r="R16" s="28" t="inlineStr">
         <is>
           <t>HIT</t>
         </is>
@@ -2967,12 +2931,10 @@
       <c r="S16" s="10" t="n">
         <v>9.5</v>
       </c>
-      <c r="T16" s="10" t="n">
-        <v/>
-      </c>
+      <c r="T16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="30" t="inlineStr">
+      <c r="A17" s="29" t="inlineStr">
         <is>
           <t>Brenen Lorient</t>
         </is>
@@ -3039,7 +3001,7 @@
       <c r="Q17" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="R17" s="29" t="inlineStr">
+      <c r="R17" s="28" t="inlineStr">
         <is>
           <t>HIT</t>
         </is>
@@ -3047,12 +3009,10 @@
       <c r="S17" s="4" t="n">
         <v>3.5</v>
       </c>
-      <c r="T17" s="4" t="n">
-        <v/>
-      </c>
+      <c r="T17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="28" t="inlineStr">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>Elyjah Freeman</t>
         </is>
@@ -3119,7 +3079,7 @@
       <c r="Q18" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="R18" s="29" t="inlineStr">
+      <c r="R18" s="28" t="inlineStr">
         <is>
           <t>HIT</t>
         </is>
@@ -3127,12 +3087,10 @@
       <c r="S18" s="10" t="n">
         <v>8.5</v>
       </c>
-      <c r="T18" s="10" t="n">
-        <v/>
-      </c>
+      <c r="T18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="30" t="inlineStr">
+      <c r="A19" s="29" t="inlineStr">
         <is>
           <t>Tahaad Pettiford</t>
         </is>
@@ -3199,7 +3157,7 @@
       <c r="Q19" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="R19" s="29" t="inlineStr">
+      <c r="R19" s="28" t="inlineStr">
         <is>
           <t>HIT</t>
         </is>
@@ -3207,12 +3165,10 @@
       <c r="S19" s="4" t="n">
         <v>5.5</v>
       </c>
-      <c r="T19" s="4" t="n">
-        <v/>
-      </c>
+      <c r="T19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="28" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>Deyton Albury</t>
         </is>
@@ -3279,7 +3235,7 @@
       <c r="Q20" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="R20" s="31" t="inlineStr">
+      <c r="R20" s="30" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
@@ -3287,12 +3243,10 @@
       <c r="S20" s="10" t="n">
         <v>-0.5</v>
       </c>
-      <c r="T20" s="10" t="n">
-        <v/>
-      </c>
+      <c r="T20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="30" t="inlineStr">
+      <c r="A21" s="29" t="inlineStr">
         <is>
           <t>Kevin Overton</t>
         </is>
@@ -3325,7 +3279,7 @@
           <t>OVER</t>
         </is>
       </c>
-      <c r="H21" s="11" t="inlineStr">
+      <c r="H21" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3359,7 +3313,7 @@
       <c r="Q21" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="R21" s="29" t="inlineStr">
+      <c r="R21" s="28" t="inlineStr">
         <is>
           <t>HIT</t>
         </is>
@@ -3367,12 +3321,10 @@
       <c r="S21" s="4" t="n">
         <v>4.5</v>
       </c>
-      <c r="T21" s="4" t="n">
-        <v/>
-      </c>
+      <c r="T21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="28" t="inlineStr">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>Tomislav Buljan</t>
         </is>
@@ -3405,7 +3357,7 @@
           <t>OVER</t>
         </is>
       </c>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="H22" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3439,7 +3391,7 @@
       <c r="Q22" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="R22" s="31" t="inlineStr">
+      <c r="R22" s="30" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
@@ -3447,12 +3399,10 @@
       <c r="S22" s="10" t="n">
         <v>-8.5</v>
       </c>
-      <c r="T22" s="10" t="n">
-        <v/>
-      </c>
+      <c r="T22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="30" t="inlineStr">
+      <c r="A23" s="29" t="inlineStr">
         <is>
           <t>Tylen Riley</t>
         </is>
@@ -3485,7 +3435,7 @@
           <t>OVER</t>
         </is>
       </c>
-      <c r="H23" s="11" t="inlineStr">
+      <c r="H23" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3519,13 +3469,13 @@
       <c r="Q23" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="R23" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R23" s="28" t="inlineStr">
+        <is>
+          <t>HIT</t>
         </is>
       </c>
       <c r="S23" s="4" t="n">
-        <v/>
+        <v>3.5</v>
       </c>
       <c r="T23" s="4" t="inlineStr">
         <is>
@@ -3534,7 +3484,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="28" t="inlineStr">
+      <c r="A24" s="27" t="inlineStr">
         <is>
           <t>Uriah Tenette</t>
         </is>
@@ -3567,7 +3517,7 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="H24" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3601,7 +3551,7 @@
       <c r="Q24" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="R24" s="29" t="inlineStr">
+      <c r="R24" s="28" t="inlineStr">
         <is>
           <t>HIT</t>
         </is>
@@ -3609,12 +3559,10 @@
       <c r="S24" s="10" t="n">
         <v>5.5</v>
       </c>
-      <c r="T24" s="10" t="n">
-        <v/>
-      </c>
+      <c r="T24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="30" t="inlineStr">
+      <c r="A25" s="29" t="inlineStr">
         <is>
           <t>Kevin Overton</t>
         </is>
@@ -3647,7 +3595,7 @@
           <t>OVER</t>
         </is>
       </c>
-      <c r="H25" s="11" t="inlineStr">
+      <c r="H25" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3681,7 +3629,7 @@
       <c r="Q25" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="R25" s="29" t="inlineStr">
+      <c r="R25" s="28" t="inlineStr">
         <is>
           <t>HIT</t>
         </is>
@@ -3689,12 +3637,10 @@
       <c r="S25" s="4" t="n">
         <v>3.5</v>
       </c>
-      <c r="T25" s="4" t="n">
-        <v/>
-      </c>
+      <c r="T25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="28" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>Tomislav Buljan</t>
         </is>
@@ -3727,7 +3673,7 @@
           <t>OVER</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="H26" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3761,7 +3707,7 @@
       <c r="Q26" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="R26" s="31" t="inlineStr">
+      <c r="R26" s="30" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
@@ -3769,12 +3715,10 @@
       <c r="S26" s="10" t="n">
         <v>-5.5</v>
       </c>
-      <c r="T26" s="10" t="n">
-        <v/>
-      </c>
+      <c r="T26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="30" t="inlineStr">
+      <c r="A27" s="29" t="inlineStr">
         <is>
           <t>Uriah Tenette</t>
         </is>
@@ -3807,7 +3751,7 @@
           <t>OVER</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="H27" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3841,13 +3785,13 @@
       <c r="Q27" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="R27" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R27" s="28" t="inlineStr">
+        <is>
+          <t>HIT</t>
         </is>
       </c>
       <c r="S27" s="4" t="n">
-        <v/>
+        <v>1.5</v>
       </c>
       <c r="T27" s="4" t="inlineStr">
         <is>
@@ -3856,7 +3800,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="28" t="inlineStr">
+      <c r="A28" s="27" t="inlineStr">
         <is>
           <t>Honor Huff</t>
         </is>
@@ -3889,7 +3833,7 @@
           <t>OVER</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="H28" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3923,7 +3867,7 @@
       <c r="Q28" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="R28" s="29" t="inlineStr">
+      <c r="R28" s="28" t="inlineStr">
         <is>
           <t>HIT</t>
         </is>
@@ -3931,12 +3875,10 @@
       <c r="S28" s="10" t="n">
         <v>6.5</v>
       </c>
-      <c r="T28" s="10" t="n">
-        <v/>
-      </c>
+      <c r="T28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="30" t="inlineStr">
+      <c r="A29" s="29" t="inlineStr">
         <is>
           <t>Boden Skunberg</t>
         </is>
@@ -3969,7 +3911,7 @@
           <t>OVER</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr">
+      <c r="H29" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4003,13 +3945,13 @@
       <c r="Q29" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="R29" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R29" s="28" t="inlineStr">
+        <is>
+          <t>HIT</t>
         </is>
       </c>
       <c r="S29" s="4" t="n">
-        <v/>
+        <v>3.5</v>
       </c>
       <c r="T29" s="4" t="inlineStr">
         <is>
@@ -4018,7 +3960,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="28" t="inlineStr">
+      <c r="A30" s="27" t="inlineStr">
         <is>
           <t>Keyshawn Hall</t>
         </is>
@@ -4051,7 +3993,7 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="H30" s="11" t="inlineStr">
+      <c r="H30" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4085,7 +4027,7 @@
       <c r="Q30" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="R30" s="29" t="inlineStr">
+      <c r="R30" s="28" t="inlineStr">
         <is>
           <t>HIT</t>
         </is>
@@ -4093,12 +4035,10 @@
       <c r="S30" s="10" t="n">
         <v>1.5</v>
       </c>
-      <c r="T30" s="10" t="n">
-        <v/>
-      </c>
+      <c r="T30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="30" t="inlineStr">
+      <c r="A31" s="29" t="inlineStr">
         <is>
           <t>Johnny Kinziger</t>
         </is>
@@ -4131,7 +4071,7 @@
           <t>OVER</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr">
+      <c r="H31" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4165,13 +4105,13 @@
       <c r="Q31" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="R31" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R31" s="30" t="inlineStr">
+        <is>
+          <t>MISS</t>
         </is>
       </c>
       <c r="S31" s="4" t="n">
-        <v/>
+        <v>-0.5</v>
       </c>
       <c r="T31" s="4" t="inlineStr">
         <is>
@@ -4180,7 +4120,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="28" t="inlineStr">
+      <c r="A32" s="27" t="inlineStr">
         <is>
           <t>Tomislav Buljan</t>
         </is>
@@ -4213,7 +4153,7 @@
           <t>OVER</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="H32" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4247,13 +4187,13 @@
       <c r="Q32" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="R32" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R32" s="30" t="inlineStr">
+        <is>
+          <t>MISS</t>
         </is>
       </c>
       <c r="S32" s="10" t="n">
-        <v/>
+        <v>-2.5</v>
       </c>
       <c r="T32" s="10" t="inlineStr">
         <is>
@@ -4262,7 +4202,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="30" t="inlineStr">
+      <c r="A33" s="29" t="inlineStr">
         <is>
           <t>Jake Hall</t>
         </is>
@@ -4295,7 +4235,7 @@
           <t>OVER</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="H33" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4329,7 +4269,7 @@
       <c r="Q33" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="R33" s="29" t="inlineStr">
+      <c r="R33" s="28" t="inlineStr">
         <is>
           <t>HIT</t>
         </is>
@@ -4337,12 +4277,10 @@
       <c r="S33" s="4" t="n">
         <v>5.5</v>
       </c>
-      <c r="T33" s="4" t="n">
-        <v/>
-      </c>
+      <c r="T33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="28" t="inlineStr">
+      <c r="A34" s="27" t="inlineStr">
         <is>
           <t>Johnny Kinziger</t>
         </is>
@@ -4375,7 +4313,7 @@
           <t>OVER</t>
         </is>
       </c>
-      <c r="H34" s="11" t="inlineStr">
+      <c r="H34" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4409,7 +4347,7 @@
       <c r="Q34" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="R34" s="31" t="inlineStr">
+      <c r="R34" s="30" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
@@ -4417,12 +4355,10 @@
       <c r="S34" s="10" t="n">
         <v>-8.5</v>
       </c>
-      <c r="T34" s="10" t="n">
-        <v/>
-      </c>
+      <c r="T34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="30" t="inlineStr">
+      <c r="A35" s="29" t="inlineStr">
         <is>
           <t>Elyjah Freeman</t>
         </is>
@@ -4455,7 +4391,7 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="H35" s="11" t="inlineStr">
+      <c r="H35" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4489,7 +4425,7 @@
       <c r="Q35" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="R35" s="29" t="inlineStr">
+      <c r="R35" s="28" t="inlineStr">
         <is>
           <t>HIT</t>
         </is>
@@ -4497,12 +4433,10 @@
       <c r="S35" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="T35" s="4" t="n">
-        <v/>
-      </c>
+      <c r="T35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="28" t="inlineStr">
+      <c r="A36" s="27" t="inlineStr">
         <is>
           <t>Boden Skunberg</t>
         </is>
@@ -4569,13 +4503,13 @@
       <c r="Q36" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R36" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R36" s="28" t="inlineStr">
+        <is>
+          <t>HIT</t>
         </is>
       </c>
       <c r="S36" s="10" t="n">
-        <v/>
+        <v>1.5</v>
       </c>
       <c r="T36" s="10" t="inlineStr">
         <is>
@@ -4584,7 +4518,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="30" t="inlineStr">
+      <c r="A37" s="29" t="inlineStr">
         <is>
           <t>Uriah Tenette</t>
         </is>
@@ -4651,13 +4585,13 @@
       <c r="Q37" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="R37" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R37" s="30" t="inlineStr">
+        <is>
+          <t>MISS</t>
         </is>
       </c>
       <c r="S37" s="4" t="n">
-        <v/>
+        <v>-1.5</v>
       </c>
       <c r="T37" s="4" t="inlineStr">
         <is>
@@ -4666,7 +4600,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="28" t="inlineStr">
+      <c r="A38" s="27" t="inlineStr">
         <is>
           <t>Elyjah Freeman</t>
         </is>
@@ -4733,7 +4667,7 @@
       <c r="Q38" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="R38" s="29" t="inlineStr">
+      <c r="R38" s="28" t="inlineStr">
         <is>
           <t>HIT</t>
         </is>
@@ -4741,12 +4675,10 @@
       <c r="S38" s="10" t="n">
         <v>4.5</v>
       </c>
-      <c r="T38" s="10" t="n">
-        <v/>
-      </c>
+      <c r="T38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="30" t="inlineStr">
+      <c r="A39" s="29" t="inlineStr">
         <is>
           <t>Boden Skunberg</t>
         </is>
@@ -4813,13 +4745,13 @@
       <c r="Q39" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="R39" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R39" s="30" t="inlineStr">
+        <is>
+          <t>MISS</t>
         </is>
       </c>
       <c r="S39" s="4" t="n">
-        <v/>
+        <v>-1.5</v>
       </c>
       <c r="T39" s="4" t="inlineStr">
         <is>
@@ -4828,7 +4760,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="28" t="inlineStr">
+      <c r="A40" s="27" t="inlineStr">
         <is>
           <t>Tahaad Pettiford</t>
         </is>
@@ -4895,13 +4827,13 @@
       <c r="Q40" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="R40" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R40" s="28" t="inlineStr">
+        <is>
+          <t>HIT</t>
         </is>
       </c>
       <c r="S40" s="10" t="n">
-        <v/>
+        <v>2.5</v>
       </c>
       <c r="T40" s="10" t="inlineStr">
         <is>
@@ -4910,7 +4842,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="30" t="inlineStr">
+      <c r="A41" s="29" t="inlineStr">
         <is>
           <t>Miles Barnstable</t>
         </is>
@@ -4977,7 +4909,7 @@
       <c r="Q41" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="R41" s="29" t="inlineStr">
+      <c r="R41" s="28" t="inlineStr">
         <is>
           <t>HIT</t>
         </is>
@@ -4985,12 +4917,10 @@
       <c r="S41" s="4" t="n">
         <v>5.5</v>
       </c>
-      <c r="T41" s="4" t="n">
-        <v/>
-      </c>
+      <c r="T41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="28" t="inlineStr">
+      <c r="A42" s="27" t="inlineStr">
         <is>
           <t>Luke Haupt</t>
         </is>
@@ -5057,13 +4987,13 @@
       <c r="Q42" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="R42" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R42" s="28" t="inlineStr">
+        <is>
+          <t>HIT</t>
         </is>
       </c>
       <c r="S42" s="10" t="n">
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="T42" s="10" t="inlineStr">
         <is>
@@ -5072,7 +5002,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="30" t="inlineStr">
+      <c r="A43" s="29" t="inlineStr">
         <is>
           <t>Miles Barnstable</t>
         </is>
@@ -5139,7 +5069,7 @@
       <c r="Q43" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="R43" s="29" t="inlineStr">
+      <c r="R43" s="28" t="inlineStr">
         <is>
           <t>HIT</t>
         </is>
@@ -5147,12 +5077,10 @@
       <c r="S43" s="4" t="n">
         <v>4.5</v>
       </c>
-      <c r="T43" s="4" t="n">
-        <v/>
-      </c>
+      <c r="T43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="28" t="inlineStr">
+      <c r="A44" s="27" t="inlineStr">
         <is>
           <t>Kevin Overton</t>
         </is>
@@ -5219,13 +5147,13 @@
       <c r="Q44" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R44" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R44" s="28" t="inlineStr">
+        <is>
+          <t>HIT</t>
         </is>
       </c>
       <c r="S44" s="10" t="n">
-        <v/>
+        <v>1.5</v>
       </c>
       <c r="T44" s="10" t="inlineStr">
         <is>
@@ -5234,7 +5162,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="30" t="inlineStr">
+      <c r="A45" s="29" t="inlineStr">
         <is>
           <t>Tylen Riley</t>
         </is>
@@ -5301,7 +5229,7 @@
       <c r="Q45" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="R45" s="31" t="inlineStr">
+      <c r="R45" s="30" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
@@ -5309,12 +5237,10 @@
       <c r="S45" s="4" t="n">
         <v>-3.5</v>
       </c>
-      <c r="T45" s="4" t="n">
-        <v/>
-      </c>
+      <c r="T45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="28" t="inlineStr">
+      <c r="A46" s="27" t="inlineStr">
         <is>
           <t>Elyjah Freeman</t>
         </is>
@@ -5381,7 +5307,7 @@
       <c r="Q46" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="R46" s="29" t="inlineStr">
+      <c r="R46" s="28" t="inlineStr">
         <is>
           <t>HIT</t>
         </is>
@@ -5389,12 +5315,10 @@
       <c r="S46" s="10" t="n">
         <v>3.5</v>
       </c>
-      <c r="T46" s="10" t="n">
-        <v/>
-      </c>
+      <c r="T46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="30" t="inlineStr">
+      <c r="A47" s="29" t="inlineStr">
         <is>
           <t>Jake Hall</t>
         </is>
@@ -5461,13 +5385,13 @@
       <c r="Q47" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="R47" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R47" s="30" t="inlineStr">
+        <is>
+          <t>MISS</t>
         </is>
       </c>
       <c r="S47" s="4" t="n">
-        <v/>
+        <v>-1.5</v>
       </c>
       <c r="T47" s="4" t="inlineStr">
         <is>
@@ -5476,7 +5400,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="28" t="inlineStr">
+      <c r="A48" s="27" t="inlineStr">
         <is>
           <t>Uriah Tenette</t>
         </is>
@@ -5543,7 +5467,7 @@
       <c r="Q48" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="R48" s="29" t="inlineStr">
+      <c r="R48" s="28" t="inlineStr">
         <is>
           <t>HIT</t>
         </is>
@@ -5551,12 +5475,10 @@
       <c r="S48" s="10" t="n">
         <v>4.5</v>
       </c>
-      <c r="T48" s="10" t="n">
-        <v/>
-      </c>
+      <c r="T48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="30" t="inlineStr">
+      <c r="A49" s="29" t="inlineStr">
         <is>
           <t>Ade Popoola</t>
         </is>
@@ -5623,7 +5545,7 @@
       <c r="Q49" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="R49" s="29" t="inlineStr">
+      <c r="R49" s="28" t="inlineStr">
         <is>
           <t>HIT</t>
         </is>
@@ -5631,12 +5553,10 @@
       <c r="S49" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="T49" s="4" t="n">
-        <v/>
-      </c>
+      <c r="T49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="28" t="inlineStr">
+      <c r="A50" s="27" t="inlineStr">
         <is>
           <t>Johnny Kinziger</t>
         </is>
@@ -5703,7 +5623,7 @@
       <c r="Q50" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="R50" s="31" t="inlineStr">
+      <c r="R50" s="30" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
@@ -5711,12 +5631,10 @@
       <c r="S50" s="10" t="n">
         <v>-7.5</v>
       </c>
-      <c r="T50" s="10" t="n">
-        <v/>
-      </c>
+      <c r="T50" s="10" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="30" t="inlineStr">
+      <c r="A51" s="29" t="inlineStr">
         <is>
           <t>Uriah Tenette</t>
         </is>
@@ -5783,7 +5701,7 @@
       <c r="Q51" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="R51" s="29" t="inlineStr">
+      <c r="R51" s="28" t="inlineStr">
         <is>
           <t>HIT</t>
         </is>
@@ -5791,12 +5709,10 @@
       <c r="S51" s="4" t="n">
         <v>4.5</v>
       </c>
-      <c r="T51" s="4" t="n">
-        <v/>
-      </c>
+      <c r="T51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="28" t="inlineStr">
+      <c r="A52" s="27" t="inlineStr">
         <is>
           <t>Jake Hall</t>
         </is>
@@ -5863,13 +5779,13 @@
       <c r="Q52" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R52" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R52" s="30" t="inlineStr">
+        <is>
+          <t>MISS</t>
         </is>
       </c>
       <c r="S52" s="10" t="n">
-        <v/>
+        <v>-0.5</v>
       </c>
       <c r="T52" s="10" t="inlineStr">
         <is>
@@ -5878,7 +5794,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="30" t="inlineStr">
+      <c r="A53" s="29" t="inlineStr">
         <is>
           <t>Elyjah Freeman</t>
         </is>
@@ -5945,7 +5861,7 @@
       <c r="Q53" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="R53" s="29" t="inlineStr">
+      <c r="R53" s="28" t="inlineStr">
         <is>
           <t>HIT</t>
         </is>
@@ -5953,12 +5869,10 @@
       <c r="S53" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="T53" s="4" t="n">
-        <v/>
-      </c>
+      <c r="T53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="28" t="inlineStr">
+      <c r="A54" s="27" t="inlineStr">
         <is>
           <t>Jasper Floyd</t>
         </is>
@@ -6025,13 +5939,13 @@
       <c r="Q54" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="R54" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R54" s="30" t="inlineStr">
+        <is>
+          <t>MISS</t>
         </is>
       </c>
       <c r="S54" s="10" t="n">
-        <v/>
+        <v>-0.5</v>
       </c>
       <c r="T54" s="10" t="inlineStr">
         <is>
@@ -6040,7 +5954,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="30" t="inlineStr">
+      <c r="A55" s="29" t="inlineStr">
         <is>
           <t>Elyjah Freeman</t>
         </is>
@@ -6107,13 +6021,13 @@
       <c r="Q55" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="R55" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R55" s="28" t="inlineStr">
+        <is>
+          <t>HIT</t>
         </is>
       </c>
       <c r="S55" s="4" t="n">
-        <v/>
+        <v>1.5</v>
       </c>
       <c r="T55" s="4" t="inlineStr">
         <is>
@@ -6122,7 +6036,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="28" t="inlineStr">
+      <c r="A56" s="27" t="inlineStr">
         <is>
           <t>Tahaad Pettiford</t>
         </is>
@@ -6189,13 +6103,13 @@
       <c r="Q56" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="R56" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R56" s="28" t="inlineStr">
+        <is>
+          <t>HIT</t>
         </is>
       </c>
       <c r="S56" s="10" t="n">
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="T56" s="10" t="inlineStr">
         <is>
@@ -6204,7 +6118,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="30" t="inlineStr">
+      <c r="A57" s="29" t="inlineStr">
         <is>
           <t>Miles Barnstable</t>
         </is>
@@ -6271,7 +6185,7 @@
       <c r="Q57" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="R57" s="29" t="inlineStr">
+      <c r="R57" s="28" t="inlineStr">
         <is>
           <t>HIT</t>
         </is>
@@ -6279,12 +6193,10 @@
       <c r="S57" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="T57" s="4" t="n">
-        <v/>
-      </c>
+      <c r="T57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="28" t="inlineStr">
+      <c r="A58" s="27" t="inlineStr">
         <is>
           <t>Elyjah Freeman</t>
         </is>
@@ -6351,13 +6263,13 @@
       <c r="Q58" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="R58" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R58" s="30" t="inlineStr">
+        <is>
+          <t>MISS</t>
         </is>
       </c>
       <c r="S58" s="10" t="n">
-        <v/>
+        <v>-0.5</v>
       </c>
       <c r="T58" s="10" t="inlineStr">
         <is>
@@ -6366,7 +6278,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="30" t="inlineStr">
+      <c r="A59" s="29" t="inlineStr">
         <is>
           <t>Tomislav Buljan</t>
         </is>
@@ -6433,7 +6345,7 @@
       <c r="Q59" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="R59" s="31" t="inlineStr">
+      <c r="R59" s="30" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
@@ -6441,12 +6353,10 @@
       <c r="S59" s="4" t="n">
         <v>-6.5</v>
       </c>
-      <c r="T59" s="4" t="n">
-        <v/>
-      </c>
+      <c r="T59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="28" t="inlineStr">
+      <c r="A60" s="27" t="inlineStr">
         <is>
           <t>Tomislav Buljan</t>
         </is>
@@ -6513,7 +6423,7 @@
       <c r="Q60" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="R60" s="31" t="inlineStr">
+      <c r="R60" s="30" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
@@ -6521,12 +6431,10 @@
       <c r="S60" s="10" t="n">
         <v>-10.5</v>
       </c>
-      <c r="T60" s="10" t="n">
-        <v/>
-      </c>
+      <c r="T60" s="10" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="30" t="inlineStr">
+      <c r="A61" s="29" t="inlineStr">
         <is>
           <t>Deyton Albury</t>
         </is>
@@ -6593,13 +6501,13 @@
       <c r="Q61" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="R61" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R61" s="28" t="inlineStr">
+        <is>
+          <t>HIT</t>
         </is>
       </c>
       <c r="S61" s="4" t="n">
-        <v/>
+        <v>4.5</v>
       </c>
       <c r="T61" s="4" t="inlineStr">
         <is>
@@ -6608,7 +6516,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="28" t="inlineStr">
+      <c r="A62" s="27" t="inlineStr">
         <is>
           <t>Chase Walker</t>
         </is>
@@ -6675,13 +6583,13 @@
       <c r="Q62" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R62" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R62" s="28" t="inlineStr">
+        <is>
+          <t>HIT</t>
         </is>
       </c>
       <c r="S62" s="10" t="n">
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="T62" s="10" t="inlineStr">
         <is>
@@ -6690,7 +6598,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="30" t="inlineStr">
+      <c r="A63" s="29" t="inlineStr">
         <is>
           <t>Johnny Kinziger</t>
         </is>
@@ -6757,7 +6665,7 @@
       <c r="Q63" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="R63" s="31" t="inlineStr">
+      <c r="R63" s="30" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
@@ -6765,12 +6673,10 @@
       <c r="S63" s="4" t="n">
         <v>-9.5</v>
       </c>
-      <c r="T63" s="4" t="n">
-        <v/>
-      </c>
+      <c r="T63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="28" t="inlineStr">
+      <c r="A64" s="27" t="inlineStr">
         <is>
           <t>Landon Wolf</t>
         </is>
@@ -6837,13 +6743,13 @@
       <c r="Q64" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="R64" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R64" s="28" t="inlineStr">
+        <is>
+          <t>HIT</t>
         </is>
       </c>
       <c r="S64" s="10" t="n">
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="T64" s="10" t="inlineStr">
         <is>
@@ -6852,7 +6758,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="30" t="inlineStr">
+      <c r="A65" s="29" t="inlineStr">
         <is>
           <t>Kevin Overton</t>
         </is>
@@ -6919,13 +6825,13 @@
       <c r="Q65" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="R65" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R65" s="28" t="inlineStr">
+        <is>
+          <t>HIT</t>
         </is>
       </c>
       <c r="S65" s="4" t="n">
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="T65" s="4" t="inlineStr">
         <is>
@@ -6934,7 +6840,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="28" t="inlineStr">
+      <c r="A66" s="27" t="inlineStr">
         <is>
           <t>Chase Walker</t>
         </is>
@@ -7001,7 +6907,7 @@
       <c r="Q66" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="R66" s="31" t="inlineStr">
+      <c r="R66" s="30" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
@@ -7009,12 +6915,10 @@
       <c r="S66" s="10" t="n">
         <v>-0.5</v>
       </c>
-      <c r="T66" s="10" t="n">
-        <v/>
-      </c>
+      <c r="T66" s="10" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="30" t="inlineStr">
+      <c r="A67" s="29" t="inlineStr">
         <is>
           <t>Keyshawn Hall</t>
         </is>
@@ -7081,13 +6985,13 @@
       <c r="Q67" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="R67" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R67" s="28" t="inlineStr">
+        <is>
+          <t>HIT</t>
         </is>
       </c>
       <c r="S67" s="4" t="n">
-        <v/>
+        <v>1.5</v>
       </c>
       <c r="T67" s="4" t="inlineStr">
         <is>
@@ -7096,7 +7000,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="28" t="inlineStr">
+      <c r="A68" s="27" t="inlineStr">
         <is>
           <t>Tylen Riley</t>
         </is>
@@ -7163,7 +7067,7 @@
       <c r="Q68" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="R68" s="31" t="inlineStr">
+      <c r="R68" s="30" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
@@ -7171,12 +7075,10 @@
       <c r="S68" s="10" t="n">
         <v>-2.5</v>
       </c>
-      <c r="T68" s="10" t="n">
-        <v/>
-      </c>
+      <c r="T68" s="10" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="30" t="inlineStr">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>Ade Popoola</t>
         </is>
@@ -7243,13 +7145,13 @@
       <c r="Q69" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="R69" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R69" s="28" t="inlineStr">
+        <is>
+          <t>HIT</t>
         </is>
       </c>
       <c r="S69" s="4" t="n">
-        <v/>
+        <v>1.5</v>
       </c>
       <c r="T69" s="4" t="inlineStr">
         <is>
@@ -7258,7 +7160,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="28" t="inlineStr">
+      <c r="A70" s="27" t="inlineStr">
         <is>
           <t>Luke Haupt</t>
         </is>
@@ -7325,13 +7227,13 @@
       <c r="Q70" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="R70" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R70" s="30" t="inlineStr">
+        <is>
+          <t>MISS</t>
         </is>
       </c>
       <c r="S70" s="10" t="n">
-        <v/>
+        <v>-2.5</v>
       </c>
       <c r="T70" s="10" t="inlineStr">
         <is>
@@ -7340,7 +7242,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="30" t="inlineStr">
+      <c r="A71" s="29" t="inlineStr">
         <is>
           <t>Jake Hall</t>
         </is>
@@ -7407,7 +7309,7 @@
       <c r="Q71" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="R71" s="31" t="inlineStr">
+      <c r="R71" s="30" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
@@ -7415,12 +7317,10 @@
       <c r="S71" s="4" t="n">
         <v>-2.5</v>
       </c>
-      <c r="T71" s="4" t="n">
-        <v/>
-      </c>
+      <c r="T71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="28" t="inlineStr">
+      <c r="A72" s="27" t="inlineStr">
         <is>
           <t>Chase Walker</t>
         </is>
@@ -7487,13 +7387,13 @@
       <c r="Q72" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="R72" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R72" s="30" t="inlineStr">
+        <is>
+          <t>MISS</t>
         </is>
       </c>
       <c r="S72" s="10" t="n">
-        <v/>
+        <v>-0.5</v>
       </c>
       <c r="T72" s="10" t="inlineStr">
         <is>
@@ -7502,7 +7402,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="30" t="inlineStr">
+      <c r="A73" s="29" t="inlineStr">
         <is>
           <t>Treysen Eaglestaff</t>
         </is>
@@ -7569,7 +7469,7 @@
       <c r="Q73" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="R73" s="31" t="inlineStr">
+      <c r="R73" s="30" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
@@ -7577,12 +7477,10 @@
       <c r="S73" s="4" t="n">
         <v>-9.5</v>
       </c>
-      <c r="T73" s="4" t="n">
-        <v/>
-      </c>
+      <c r="T73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="28" t="inlineStr">
+      <c r="A74" s="27" t="inlineStr">
         <is>
           <t>Tylen Riley</t>
         </is>
@@ -7649,13 +7547,13 @@
       <c r="Q74" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="R74" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R74" s="28" t="inlineStr">
+        <is>
+          <t>HIT</t>
         </is>
       </c>
       <c r="S74" s="10" t="n">
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="T74" s="10" t="inlineStr">
         <is>
@@ -7664,7 +7562,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="30" t="inlineStr">
+      <c r="A75" s="29" t="inlineStr">
         <is>
           <t>Kevin Overton</t>
         </is>
@@ -7731,7 +7629,7 @@
       <c r="Q75" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="R75" s="29" t="inlineStr">
+      <c r="R75" s="28" t="inlineStr">
         <is>
           <t>HIT</t>
         </is>
@@ -7739,12 +7637,10 @@
       <c r="S75" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="T75" s="4" t="n">
-        <v/>
-      </c>
+      <c r="T75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="28" t="inlineStr">
+      <c r="A76" s="27" t="inlineStr">
         <is>
           <t>Tylen Riley</t>
         </is>
@@ -7811,13 +7707,13 @@
       <c r="Q76" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="R76" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R76" s="30" t="inlineStr">
+        <is>
+          <t>MISS</t>
         </is>
       </c>
       <c r="S76" s="10" t="n">
-        <v/>
+        <v>-4.5</v>
       </c>
       <c r="T76" s="10" t="inlineStr">
         <is>
@@ -7826,7 +7722,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="30" t="inlineStr">
+      <c r="A77" s="29" t="inlineStr">
         <is>
           <t>Johnny Kinziger</t>
         </is>
@@ -7893,13 +7789,13 @@
       <c r="Q77" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="R77" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R77" s="30" t="inlineStr">
+        <is>
+          <t>MISS</t>
         </is>
       </c>
       <c r="S77" s="4" t="n">
-        <v/>
+        <v>-1.5</v>
       </c>
       <c r="T77" s="4" t="inlineStr">
         <is>
@@ -7908,7 +7804,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="28" t="inlineStr">
+      <c r="A78" s="27" t="inlineStr">
         <is>
           <t>Jake Hall</t>
         </is>
@@ -7975,7 +7871,7 @@
       <c r="Q78" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="R78" s="31" t="inlineStr">
+      <c r="R78" s="30" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
@@ -7983,12 +7879,10 @@
       <c r="S78" s="10" t="n">
         <v>-1.5</v>
       </c>
-      <c r="T78" s="10" t="n">
-        <v/>
-      </c>
+      <c r="T78" s="10" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="30" t="inlineStr">
+      <c r="A79" s="29" t="inlineStr">
         <is>
           <t>Miles Barnstable</t>
         </is>
@@ -8055,13 +7949,13 @@
       <c r="Q79" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R79" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R79" s="30" t="inlineStr">
+        <is>
+          <t>MISS</t>
         </is>
       </c>
       <c r="S79" s="4" t="n">
-        <v/>
+        <v>-0.5</v>
       </c>
       <c r="T79" s="4" t="inlineStr">
         <is>
@@ -8070,7 +7964,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="28" t="inlineStr">
+      <c r="A80" s="27" t="inlineStr">
         <is>
           <t>Tomislav Buljan</t>
         </is>
@@ -8137,13 +8031,13 @@
       <c r="Q80" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="R80" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R80" s="30" t="inlineStr">
+        <is>
+          <t>MISS</t>
         </is>
       </c>
       <c r="S80" s="10" t="n">
-        <v/>
+        <v>-0.5</v>
       </c>
       <c r="T80" s="10" t="inlineStr">
         <is>
@@ -8152,7 +8046,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="30" t="inlineStr">
+      <c r="A81" s="29" t="inlineStr">
         <is>
           <t>Jake Hall</t>
         </is>
@@ -8219,13 +8113,13 @@
       <c r="Q81" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="R81" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R81" s="30" t="inlineStr">
+        <is>
+          <t>MISS</t>
         </is>
       </c>
       <c r="S81" s="4" t="n">
-        <v/>
+        <v>-0.5</v>
       </c>
       <c r="T81" s="4" t="inlineStr">
         <is>
@@ -8234,7 +8128,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="28" t="inlineStr">
+      <c r="A82" s="27" t="inlineStr">
         <is>
           <t>Tylen Riley</t>
         </is>
@@ -8301,13 +8195,13 @@
       <c r="Q82" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="R82" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R82" s="30" t="inlineStr">
+        <is>
+          <t>MISS</t>
         </is>
       </c>
       <c r="S82" s="10" t="n">
-        <v/>
+        <v>-0.5</v>
       </c>
       <c r="T82" s="10" t="inlineStr">
         <is>
@@ -8316,7 +8210,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="30" t="inlineStr">
+      <c r="A83" s="29" t="inlineStr">
         <is>
           <t>Uriah Tenette</t>
         </is>
@@ -8383,13 +8277,13 @@
       <c r="Q83" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="R83" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R83" s="28" t="inlineStr">
+        <is>
+          <t>HIT</t>
         </is>
       </c>
       <c r="S83" s="4" t="n">
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="T83" s="4" t="inlineStr">
         <is>
@@ -8398,7 +8292,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="28" t="inlineStr">
+      <c r="A84" s="27" t="inlineStr">
         <is>
           <t>Tomislav Buljan</t>
         </is>
@@ -8465,13 +8359,13 @@
       <c r="Q84" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="R84" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R84" s="30" t="inlineStr">
+        <is>
+          <t>MISS</t>
         </is>
       </c>
       <c r="S84" s="10" t="n">
-        <v/>
+        <v>-4.5</v>
       </c>
       <c r="T84" s="10" t="inlineStr">
         <is>
@@ -8480,7 +8374,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="30" t="inlineStr">
+      <c r="A85" s="29" t="inlineStr">
         <is>
           <t>Luke Haupt</t>
         </is>
@@ -8547,13 +8441,13 @@
       <c r="Q85" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="R85" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R85" s="30" t="inlineStr">
+        <is>
+          <t>MISS</t>
         </is>
       </c>
       <c r="S85" s="4" t="n">
-        <v/>
+        <v>-3.5</v>
       </c>
       <c r="T85" s="4" t="inlineStr">
         <is>
@@ -8562,7 +8456,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="28" t="inlineStr">
+      <c r="A86" s="27" t="inlineStr">
         <is>
           <t>Brenen Lorient</t>
         </is>
@@ -8629,13 +8523,13 @@
       <c r="Q86" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="R86" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R86" s="28" t="inlineStr">
+        <is>
+          <t>HIT</t>
         </is>
       </c>
       <c r="S86" s="10" t="n">
-        <v/>
+        <v>1.5</v>
       </c>
       <c r="T86" s="10" t="inlineStr">
         <is>
@@ -8644,7 +8538,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="30" t="inlineStr">
+      <c r="A87" s="29" t="inlineStr">
         <is>
           <t>Tomislav Buljan</t>
         </is>
@@ -8711,13 +8605,13 @@
       <c r="Q87" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="R87" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R87" s="30" t="inlineStr">
+        <is>
+          <t>MISS</t>
         </is>
       </c>
       <c r="S87" s="4" t="n">
-        <v/>
+        <v>-3.5</v>
       </c>
       <c r="T87" s="4" t="inlineStr">
         <is>
@@ -8726,7 +8620,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="28" t="inlineStr">
+      <c r="A88" s="27" t="inlineStr">
         <is>
           <t>Luke Haupt</t>
         </is>
@@ -8793,7 +8687,7 @@
       <c r="Q88" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="R88" s="29" t="inlineStr">
+      <c r="R88" s="28" t="inlineStr">
         <is>
           <t>HIT</t>
         </is>
@@ -8801,12 +8695,10 @@
       <c r="S88" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="T88" s="10" t="n">
-        <v/>
-      </c>
+      <c r="T88" s="10" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="30" t="inlineStr">
+      <c r="A89" s="29" t="inlineStr">
         <is>
           <t>Miles Barnstable</t>
         </is>
@@ -8873,13 +8765,13 @@
       <c r="Q89" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="R89" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R89" s="28" t="inlineStr">
+        <is>
+          <t>HIT</t>
         </is>
       </c>
       <c r="S89" s="4" t="n">
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="T89" s="4" t="inlineStr">
         <is>
@@ -8888,7 +8780,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="28" t="inlineStr">
+      <c r="A90" s="27" t="inlineStr">
         <is>
           <t>Ade Popoola</t>
         </is>
@@ -8955,13 +8847,13 @@
       <c r="Q90" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R90" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R90" s="28" t="inlineStr">
+        <is>
+          <t>HIT</t>
         </is>
       </c>
       <c r="S90" s="10" t="n">
-        <v/>
+        <v>1.5</v>
       </c>
       <c r="T90" s="10" t="inlineStr">
         <is>
@@ -8970,7 +8862,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="30" t="inlineStr">
+      <c r="A91" s="29" t="inlineStr">
         <is>
           <t>Uriah Tenette</t>
         </is>
@@ -9037,13 +8929,13 @@
       <c r="Q91" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="R91" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R91" s="28" t="inlineStr">
+        <is>
+          <t>HIT</t>
         </is>
       </c>
       <c r="S91" s="4" t="n">
-        <v/>
+        <v>1.5</v>
       </c>
       <c r="T91" s="4" t="inlineStr">
         <is>
@@ -9052,7 +8944,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="28" t="inlineStr">
+      <c r="A92" s="27" t="inlineStr">
         <is>
           <t>Elyjah Freeman</t>
         </is>
@@ -9119,13 +9011,13 @@
       <c r="Q92" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="R92" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R92" s="30" t="inlineStr">
+        <is>
+          <t>MISS</t>
         </is>
       </c>
       <c r="S92" s="10" t="n">
-        <v/>
+        <v>-2.5</v>
       </c>
       <c r="T92" s="10" t="inlineStr">
         <is>
@@ -9134,7 +9026,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="30" t="inlineStr">
+      <c r="A93" s="29" t="inlineStr">
         <is>
           <t>Deyton Albury</t>
         </is>
@@ -9201,13 +9093,13 @@
       <c r="Q93" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R93" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R93" s="30" t="inlineStr">
+        <is>
+          <t>MISS</t>
         </is>
       </c>
       <c r="S93" s="4" t="n">
-        <v/>
+        <v>-0.5</v>
       </c>
       <c r="T93" s="4" t="inlineStr">
         <is>
@@ -9216,7 +9108,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="28" t="inlineStr">
+      <c r="A94" s="27" t="inlineStr">
         <is>
           <t>Treysen Eaglestaff</t>
         </is>
@@ -9283,13 +9175,13 @@
       <c r="Q94" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="R94" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R94" s="28" t="inlineStr">
+        <is>
+          <t>HIT</t>
         </is>
       </c>
       <c r="S94" s="10" t="n">
-        <v/>
+        <v>10.5</v>
       </c>
       <c r="T94" s="10" t="inlineStr">
         <is>
@@ -9298,7 +9190,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="30" t="inlineStr">
+      <c r="A95" s="29" t="inlineStr">
         <is>
           <t>Luke Haupt</t>
         </is>
@@ -9365,13 +9257,13 @@
       <c r="Q95" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="R95" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R95" s="30" t="inlineStr">
+        <is>
+          <t>MISS</t>
         </is>
       </c>
       <c r="S95" s="4" t="n">
-        <v/>
+        <v>-0.5</v>
       </c>
       <c r="T95" s="4" t="inlineStr">
         <is>
@@ -9380,7 +9272,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="28" t="inlineStr">
+      <c r="A96" s="27" t="inlineStr">
         <is>
           <t>Luke Haupt</t>
         </is>
@@ -9447,13 +9339,13 @@
       <c r="Q96" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="R96" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R96" s="30" t="inlineStr">
+        <is>
+          <t>MISS</t>
         </is>
       </c>
       <c r="S96" s="10" t="n">
-        <v/>
+        <v>-3.5</v>
       </c>
       <c r="T96" s="10" t="inlineStr">
         <is>
@@ -9462,7 +9354,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="30" t="inlineStr">
+      <c r="A97" s="29" t="inlineStr">
         <is>
           <t>Ade Popoola</t>
         </is>
@@ -9529,13 +9421,13 @@
       <c r="Q97" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="R97" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R97" s="28" t="inlineStr">
+        <is>
+          <t>HIT</t>
         </is>
       </c>
       <c r="S97" s="4" t="n">
-        <v/>
+        <v>1.5</v>
       </c>
       <c r="T97" s="4" t="inlineStr">
         <is>
@@ -9544,7 +9436,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="28" t="inlineStr">
+      <c r="A98" s="27" t="inlineStr">
         <is>
           <t>Jake Hall</t>
         </is>
@@ -9611,7 +9503,7 @@
       <c r="Q98" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="R98" s="29" t="inlineStr">
+      <c r="R98" s="28" t="inlineStr">
         <is>
           <t>HIT</t>
         </is>
@@ -9619,12 +9511,10 @@
       <c r="S98" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="T98" s="10" t="n">
-        <v/>
-      </c>
+      <c r="T98" s="10" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="30" t="inlineStr">
+      <c r="A99" s="29" t="inlineStr">
         <is>
           <t>Honor Huff</t>
         </is>
@@ -9691,13 +9581,13 @@
       <c r="Q99" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="R99" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R99" s="28" t="inlineStr">
+        <is>
+          <t>HIT</t>
         </is>
       </c>
       <c r="S99" s="4" t="n">
-        <v/>
+        <v>4.5</v>
       </c>
       <c r="T99" s="4" t="inlineStr">
         <is>
@@ -9706,7 +9596,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="28" t="inlineStr">
+      <c r="A100" s="27" t="inlineStr">
         <is>
           <t>Miles Barnstable</t>
         </is>
@@ -9773,13 +9663,13 @@
       <c r="Q100" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="R100" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R100" s="28" t="inlineStr">
+        <is>
+          <t>HIT</t>
         </is>
       </c>
       <c r="S100" s="10" t="n">
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="T100" s="10" t="inlineStr">
         <is>
@@ -9788,7 +9678,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="30" t="inlineStr">
+      <c r="A101" s="29" t="inlineStr">
         <is>
           <t>Deyton Albury</t>
         </is>
@@ -9855,7 +9745,7 @@
       <c r="Q101" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="R101" s="29" t="inlineStr">
+      <c r="R101" s="28" t="inlineStr">
         <is>
           <t>HIT</t>
         </is>
@@ -9863,12 +9753,10 @@
       <c r="S101" s="4" t="n">
         <v>3.5</v>
       </c>
-      <c r="T101" s="4" t="n">
-        <v/>
-      </c>
+      <c r="T101" s="4" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="28" t="inlineStr">
+      <c r="A102" s="27" t="inlineStr">
         <is>
           <t>Luke Haupt</t>
         </is>
@@ -9935,13 +9823,13 @@
       <c r="Q102" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="R102" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R102" s="30" t="inlineStr">
+        <is>
+          <t>MISS</t>
         </is>
       </c>
       <c r="S102" s="10" t="n">
-        <v/>
+        <v>-0.5</v>
       </c>
       <c r="T102" s="10" t="inlineStr">
         <is>
@@ -9950,7 +9838,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="30" t="inlineStr">
+      <c r="A103" s="29" t="inlineStr">
         <is>
           <t>Luke Haupt</t>
         </is>
@@ -10017,13 +9905,13 @@
       <c r="Q103" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="R103" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R103" s="28" t="inlineStr">
+        <is>
+          <t>HIT</t>
         </is>
       </c>
       <c r="S103" s="4" t="n">
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="T103" s="4" t="inlineStr">
         <is>
@@ -10032,7 +9920,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="28" t="inlineStr">
+      <c r="A104" s="27" t="inlineStr">
         <is>
           <t>Jasper Floyd</t>
         </is>
@@ -10099,13 +9987,13 @@
       <c r="Q104" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="R104" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R104" s="30" t="inlineStr">
+        <is>
+          <t>MISS</t>
         </is>
       </c>
       <c r="S104" s="10" t="n">
-        <v/>
+        <v>-1.5</v>
       </c>
       <c r="T104" s="10" t="inlineStr">
         <is>
@@ -10114,7 +10002,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="30" t="inlineStr">
+      <c r="A105" s="29" t="inlineStr">
         <is>
           <t>Tahaad Pettiford</t>
         </is>
@@ -10181,13 +10069,13 @@
       <c r="Q105" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="R105" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R105" s="28" t="inlineStr">
+        <is>
+          <t>HIT</t>
         </is>
       </c>
       <c r="S105" s="4" t="n">
-        <v/>
+        <v>1.5</v>
       </c>
       <c r="T105" s="4" t="inlineStr">
         <is>
@@ -10196,7 +10084,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="28" t="inlineStr">
+      <c r="A106" s="27" t="inlineStr">
         <is>
           <t>Tahaad Pettiford</t>
         </is>
@@ -10263,13 +10151,13 @@
       <c r="Q106" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="R106" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R106" s="30" t="inlineStr">
+        <is>
+          <t>MISS</t>
         </is>
       </c>
       <c r="S106" s="10" t="n">
-        <v/>
+        <v>-2.5</v>
       </c>
       <c r="T106" s="10" t="inlineStr">
         <is>
@@ -10278,7 +10166,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="30" t="inlineStr">
+      <c r="A107" s="29" t="inlineStr">
         <is>
           <t>Deyton Albury</t>
         </is>
@@ -10345,13 +10233,13 @@
       <c r="Q107" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="R107" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R107" s="30" t="inlineStr">
+        <is>
+          <t>MISS</t>
         </is>
       </c>
       <c r="S107" s="4" t="n">
-        <v/>
+        <v>-0.5</v>
       </c>
       <c r="T107" s="4" t="inlineStr">
         <is>
@@ -10360,7 +10248,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="28" t="inlineStr">
+      <c r="A108" s="27" t="inlineStr">
         <is>
           <t>Boden Skunberg</t>
         </is>
@@ -10427,7 +10315,7 @@
       <c r="Q108" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="R108" s="31" t="inlineStr">
+      <c r="R108" s="30" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
@@ -10435,12 +10323,10 @@
       <c r="S108" s="10" t="n">
         <v>-2.5</v>
       </c>
-      <c r="T108" s="10" t="n">
-        <v/>
-      </c>
+      <c r="T108" s="10" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="30" t="inlineStr">
+      <c r="A109" s="29" t="inlineStr">
         <is>
           <t>Keyshawn Hall</t>
         </is>
@@ -10507,13 +10393,13 @@
       <c r="Q109" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="R109" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R109" s="28" t="inlineStr">
+        <is>
+          <t>HIT</t>
         </is>
       </c>
       <c r="S109" s="4" t="n">
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="T109" s="4" t="inlineStr">
         <is>
@@ -10522,7 +10408,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="28" t="inlineStr">
+      <c r="A110" s="27" t="inlineStr">
         <is>
           <t>Keyshawn Hall</t>
         </is>
@@ -10589,13 +10475,13 @@
       <c r="Q110" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="R110" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R110" s="30" t="inlineStr">
+        <is>
+          <t>MISS</t>
         </is>
       </c>
       <c r="S110" s="10" t="n">
-        <v/>
+        <v>-0.5</v>
       </c>
       <c r="T110" s="10" t="inlineStr">
         <is>
@@ -10604,7 +10490,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="30" t="inlineStr">
+      <c r="A111" s="29" t="inlineStr">
         <is>
           <t>Jake Hall</t>
         </is>
@@ -10671,13 +10557,13 @@
       <c r="Q111" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="R111" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R111" s="28" t="inlineStr">
+        <is>
+          <t>HIT</t>
         </is>
       </c>
       <c r="S111" s="4" t="n">
-        <v/>
+        <v>2.5</v>
       </c>
       <c r="T111" s="4" t="inlineStr">
         <is>
@@ -10686,7 +10572,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="28" t="inlineStr">
+      <c r="A112" s="27" t="inlineStr">
         <is>
           <t>Miles Barnstable</t>
         </is>
@@ -10753,13 +10639,13 @@
       <c r="Q112" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="R112" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R112" s="30" t="inlineStr">
+        <is>
+          <t>MISS</t>
         </is>
       </c>
       <c r="S112" s="10" t="n">
-        <v/>
+        <v>-3.5</v>
       </c>
       <c r="T112" s="10" t="inlineStr">
         <is>
@@ -10768,7 +10654,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="30" t="inlineStr">
+      <c r="A113" s="29" t="inlineStr">
         <is>
           <t>Tylen Riley</t>
         </is>
@@ -10835,13 +10721,13 @@
       <c r="Q113" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="R113" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R113" s="28" t="inlineStr">
+        <is>
+          <t>HIT</t>
         </is>
       </c>
       <c r="S113" s="4" t="n">
-        <v/>
+        <v>1.5</v>
       </c>
       <c r="T113" s="4" t="inlineStr">
         <is>
@@ -10850,7 +10736,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="28" t="inlineStr">
+      <c r="A114" s="27" t="inlineStr">
         <is>
           <t>Ade Popoola</t>
         </is>
@@ -10917,13 +10803,13 @@
       <c r="Q114" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="R114" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R114" s="30" t="inlineStr">
+        <is>
+          <t>MISS</t>
         </is>
       </c>
       <c r="S114" s="10" t="n">
-        <v/>
+        <v>-1.5</v>
       </c>
       <c r="T114" s="10" t="inlineStr">
         <is>
@@ -10932,7 +10818,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="30" t="inlineStr">
+      <c r="A115" s="29" t="inlineStr">
         <is>
           <t>Keyshawn Hall</t>
         </is>
@@ -10999,13 +10885,13 @@
       <c r="Q115" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="R115" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R115" s="28" t="inlineStr">
+        <is>
+          <t>HIT</t>
         </is>
       </c>
       <c r="S115" s="4" t="n">
-        <v/>
+        <v>9.5</v>
       </c>
       <c r="T115" s="4" t="inlineStr">
         <is>
@@ -11014,7 +10900,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="28" t="inlineStr">
+      <c r="A116" s="27" t="inlineStr">
         <is>
           <t>Tahaad Pettiford</t>
         </is>
@@ -11081,13 +10967,13 @@
       <c r="Q116" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="R116" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R116" s="28" t="inlineStr">
+        <is>
+          <t>HIT</t>
         </is>
       </c>
       <c r="S116" s="10" t="n">
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="T116" s="10" t="inlineStr">
         <is>
@@ -11096,7 +10982,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="30" t="inlineStr">
+      <c r="A117" s="29" t="inlineStr">
         <is>
           <t>Tahaad Pettiford</t>
         </is>
@@ -11163,13 +11049,13 @@
       <c r="Q117" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="R117" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R117" s="30" t="inlineStr">
+        <is>
+          <t>MISS</t>
         </is>
       </c>
       <c r="S117" s="4" t="n">
-        <v/>
+        <v>-0.5</v>
       </c>
       <c r="T117" s="4" t="inlineStr">
         <is>
@@ -11178,7 +11064,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="28" t="inlineStr">
+      <c r="A118" s="27" t="inlineStr">
         <is>
           <t>Kevin Overton</t>
         </is>
@@ -11245,13 +11131,13 @@
       <c r="Q118" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="R118" s="32" t="inlineStr">
-        <is>
-          <t>VOID</t>
+      <c r="R118" s="30" t="inlineStr">
+        <is>
+          <t>MISS</t>
         </is>
       </c>
       <c r="S118" s="10" t="n">
-        <v/>
+        <v>-0.5</v>
       </c>
       <c r="T118" s="10" t="inlineStr">
         <is>
@@ -11327,7 +11213,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="33" t="inlineStr">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>Goblin</t>
         </is>
@@ -11341,23 +11227,23 @@
         <v>57</v>
       </c>
       <c r="D2" s="8" t="n">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F2" s="8" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G2" s="8" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>0.6470588235294118</v>
+        <v>0.631578947368421</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="34" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
@@ -11371,45 +11257,45 @@
         <v>60</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G3" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>0.5555555555555556</v>
+        <v>0</v>
+      </c>
+      <c r="H3" s="11" t="n">
+        <v>0.45</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr"/>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr"/>
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="C4" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="D4" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="E4" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="11" t="n">
+      <c r="D4" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="E4" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="G4" s="11" t="n">
-        <v>24</v>
-      </c>
-      <c r="H4" s="13" t="n">
-        <v>0.1111111111111111</v>
+      <c r="F4" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="G4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="11" t="n">
+        <v>0.2424242424242424</v>
       </c>
     </row>
     <row r="5">
@@ -11516,7 +11402,7 @@
           <t>Tier A</t>
         </is>
       </c>
-      <c r="B2" s="35" t="inlineStr">
+      <c r="B2" s="33" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
@@ -11547,7 +11433,7 @@
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr"/>
-      <c r="B3" s="33" t="inlineStr">
+      <c r="B3" s="31" t="inlineStr">
         <is>
           <t>Goblin</t>
         </is>
@@ -11578,7 +11464,7 @@
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr"/>
-      <c r="B4" s="34" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
@@ -11609,7 +11495,7 @@
     </row>
     <row r="5">
       <c r="A5" s="15" t="inlineStr"/>
-      <c r="B5" s="36" t="inlineStr"/>
+      <c r="B5" s="34" t="inlineStr"/>
       <c r="C5" s="15" t="inlineStr">
         <is>
           <t>UNDER</t>
@@ -11635,43 +11521,43 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Tier B</t>
         </is>
       </c>
-      <c r="B6" s="37" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="F6" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F6" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="H6" s="11" t="n">
+      <c r="G6" s="12" t="n">
         <v>5</v>
       </c>
+      <c r="H6" s="12" t="n">
+        <v>0</v>
+      </c>
       <c r="I6" s="16" t="n">
-        <v>0.7</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr"/>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="31" t="inlineStr">
         <is>
           <t>Goblin</t>
         </is>
@@ -11685,24 +11571,24 @@
         <v>11</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F7" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G7" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="G7" s="8" t="n">
-        <v>2</v>
-      </c>
       <c r="H7" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I7" s="16" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>0.6363636363636364</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr"/>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
@@ -11732,35 +11618,35 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr"/>
-      <c r="B9" s="37" t="inlineStr"/>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr"/>
+      <c r="B9" s="35" t="inlineStr"/>
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="11" t="n">
+      <c r="F9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="13" t="n">
+      <c r="H9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr"/>
-      <c r="B10" s="36" t="inlineStr"/>
+      <c r="B10" s="34" t="inlineStr"/>
       <c r="C10" s="15" t="inlineStr">
         <is>
           <t>UNDER</t>
@@ -11791,7 +11677,7 @@
           <t>Tier C</t>
         </is>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
@@ -11805,24 +11691,24 @@
         <v>33</v>
       </c>
       <c r="E11" s="21" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F11" s="21" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="G11" s="21" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H11" s="21" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.5625</v>
+        <v>0.6060606060606061</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr"/>
-      <c r="B12" s="33" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>Goblin</t>
         </is>
@@ -11836,22 +11722,24 @@
         <v>15</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="I12" s="24" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="I12" s="16" t="n">
+        <v>0.6666666666666666</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr"/>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
@@ -11865,51 +11753,51 @@
         <v>18</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr"/>
+      <c r="B14" s="35" t="inlineStr"/>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I13" s="5" t="n">
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr"/>
-      <c r="B14" s="37" t="inlineStr"/>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" s="11" t="n">
+      <c r="G14" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="F14" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H14" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" s="13" t="n">
-        <v>0.125</v>
+      <c r="H14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr"/>
-      <c r="B15" s="36" t="inlineStr"/>
+      <c r="B15" s="34" t="inlineStr"/>
       <c r="C15" s="15" t="inlineStr">
         <is>
           <t>UNDER</t>
@@ -11940,7 +11828,7 @@
           <t>Tier D</t>
         </is>
       </c>
-      <c r="B16" s="39" t="inlineStr">
+      <c r="B16" s="37" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
@@ -11954,24 +11842,24 @@
         <v>50</v>
       </c>
       <c r="E16" s="23" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="F16" s="23" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="G16" s="23" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="H16" s="23" t="n">
-        <v>42</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>0.44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr"/>
-      <c r="B17" s="33" t="inlineStr">
+      <c r="B17" s="31" t="inlineStr">
         <is>
           <t>Goblin</t>
         </is>
@@ -11985,22 +11873,24 @@
         <v>20</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="I17" s="24" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr"/>
-      <c r="B18" s="34" t="inlineStr">
+      <c r="B18" s="32" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
@@ -12014,49 +11904,51 @@
         <v>30</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr"/>
+      <c r="B19" s="35" t="inlineStr"/>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="I18" s="5" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr"/>
-      <c r="B19" s="37" t="inlineStr"/>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="n">
+      <c r="E19" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="E19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="11" t="n">
-        <v>22</v>
-      </c>
-      <c r="I19" s="24" t="inlineStr"/>
+      <c r="F19" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>0.2727272727272727</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr"/>
-      <c r="B20" s="36" t="inlineStr"/>
+      <c r="B20" s="34" t="inlineStr"/>
       <c r="C20" s="15" t="inlineStr">
         <is>
           <t>UNDER</t>
@@ -12148,7 +12040,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="34" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>pts</t>
         </is>
@@ -12162,45 +12054,45 @@
         <v>37</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="E2" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="F2" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="G2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>0.5135135135135135</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr"/>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="D3" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="E3" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="F3" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="F2" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr"/>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="n">
-        <v>29</v>
-      </c>
-      <c r="D3" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="E3" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G3" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>0.5882352941176471</v>
+      <c r="G3" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="11" t="n">
+        <v>0.4827586206896552</v>
       </c>
     </row>
     <row r="4">
@@ -12232,57 +12124,57 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>pr</t>
-        </is>
-      </c>
-      <c r="B5" s="40" t="inlineStr">
+          <t>reb</t>
+        </is>
+      </c>
+      <c r="B5" s="38" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="G5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>0.5263157894736842</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr"/>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="E5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="13" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr"/>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="13" t="n">
-        <v>0</v>
+      <c r="G6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="11" t="n">
+        <v>0.4705882352941176</v>
       </c>
     </row>
     <row r="7">
@@ -12293,537 +12185,545 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t>ast</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F8" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="G8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="F9" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="G9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t>fg3m</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="11" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr"/>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="11" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>pa</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E12" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F12" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="11" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="11" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr"/>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="5" t="n">
+      <c r="F14" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>pr</t>
+        </is>
+      </c>
+      <c r="B15" s="38" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="11" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr"/>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr"/>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5" t="n">
         <v>0.6</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="34" t="inlineStr">
-        <is>
-          <t>pa</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="32" t="inlineStr">
+        <is>
+          <t>ra</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="C8" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="D8" s="10" t="n">
+      <c r="C18" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="F18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="16" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr"/>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F19" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="16" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr"/>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="G8" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H8" s="13" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr"/>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D9" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="H9" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr"/>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="n">
+      <c r="D20" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="E20" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="E10" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>pra</t>
-        </is>
-      </c>
-      <c r="B11" s="40" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="16" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr"/>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr"/>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="E13" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="16" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="34" t="inlineStr">
-        <is>
-          <t>ra</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="D14" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F14" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H14" s="16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr"/>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="H15" s="24" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr"/>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="E16" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>reb</t>
-        </is>
-      </c>
-      <c r="B17" s="40" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="H17" s="16" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr"/>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="D18" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="H18" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr"/>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="34" t="inlineStr">
-        <is>
-          <t>ast</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="D20" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="10" t="n">
-        <v>17</v>
+      <c r="F20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="H20" s="16" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr"/>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>pra</t>
+        </is>
+      </c>
+      <c r="B21" s="38" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr"/>
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="C21" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="D21" s="11" t="n">
+      <c r="C22" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="F22" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="H21" s="16" t="n">
+      <c r="G22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr"/>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="14" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="34" t="inlineStr">
+      <c r="G23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="16" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="32" t="inlineStr">
         <is>
           <t>tov</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="C22" s="10" t="n">
+      <c r="C24" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="10" t="n">
+      <c r="D24" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="10" t="n">
+      <c r="F24" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="10" t="n">
+      <c r="G24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr"/>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="16" t="n">
+      <c r="D25" s="12" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr"/>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="n">
+      <c r="E25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="11" t="n">
+      <c r="G25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr"/>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="24" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr"/>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="n">
+      <c r="D26" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="14" t="n">
+      <c r="E26" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E24" s="14" t="n">
+      <c r="F26" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>fg3m</t>
-        </is>
-      </c>
-      <c r="B25" s="40" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="H25" s="24" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr"/>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="D26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="H26" s="24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12849,44 +12749,44 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="25" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>bet_direction</t>
         </is>
       </c>
-      <c r="B1" s="25" t="inlineStr">
+      <c r="B1" s="24" t="inlineStr">
         <is>
           <t>total</t>
         </is>
       </c>
-      <c r="C1" s="25" t="inlineStr">
+      <c r="C1" s="24" t="inlineStr">
         <is>
           <t>hit</t>
         </is>
       </c>
-      <c r="D1" s="25" t="inlineStr">
+      <c r="D1" s="24" t="inlineStr">
         <is>
           <t>miss</t>
         </is>
       </c>
-      <c r="E1" s="25" t="inlineStr">
+      <c r="E1" s="24" t="inlineStr">
         <is>
           <t>void</t>
         </is>
       </c>
-      <c r="F1" s="25" t="inlineStr">
+      <c r="F1" s="24" t="inlineStr">
         <is>
           <t>decided</t>
         </is>
       </c>
-      <c r="G1" s="25" t="inlineStr">
+      <c r="G1" s="24" t="inlineStr">
         <is>
           <t>hit_rate</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="28" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
@@ -12895,23 +12795,23 @@
         <v>90</v>
       </c>
       <c r="C2" s="10" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>26</v>
-      </c>
-      <c r="G2" s="13" t="n">
-        <v>0.4615</v>
+        <v>90</v>
+      </c>
+      <c r="G2" s="11" t="n">
+        <v>0.4889</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="29" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
@@ -12960,49 +12860,49 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="26" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>Minutes Tier</t>
         </is>
       </c>
-      <c r="B1" s="26" t="inlineStr">
+      <c r="B1" s="25" t="inlineStr">
         <is>
           <t>Direction</t>
         </is>
       </c>
-      <c r="C1" s="26" t="inlineStr">
+      <c r="C1" s="25" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="D1" s="26" t="inlineStr">
+      <c r="D1" s="25" t="inlineStr">
         <is>
           <t>Decided</t>
         </is>
       </c>
-      <c r="E1" s="26" t="inlineStr">
+      <c r="E1" s="25" t="inlineStr">
         <is>
           <t>Hits</t>
         </is>
       </c>
-      <c r="F1" s="26" t="inlineStr">
+      <c r="F1" s="25" t="inlineStr">
         <is>
           <t>Misses</t>
         </is>
       </c>
-      <c r="G1" s="26" t="inlineStr">
+      <c r="G1" s="25" t="inlineStr">
         <is>
           <t>Voids</t>
         </is>
       </c>
-      <c r="H1" s="26" t="inlineStr">
+      <c r="H1" s="25" t="inlineStr">
         <is>
           <t>Hit Rate</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="34" t="n">
+      <c r="A2" s="32" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="9" t="inlineStr">
@@ -13014,45 +12914,45 @@
         <v>43</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F2" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="G2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>0.5348837209302325</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr"/>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="D3" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="E3" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="G2" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>0.5757575757575758</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr"/>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="n">
-        <v>31</v>
-      </c>
-      <c r="D3" s="11" t="n">
-        <v>21</v>
-      </c>
-      <c r="E3" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="G3" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="H3" s="13" t="n">
-        <v>0.4761904761904762</v>
+      <c r="F3" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="G3" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="11" t="n">
+        <v>0.4516129032258064</v>
       </c>
     </row>
     <row r="4">
@@ -13085,7 +12985,7 @@
       <c r="A5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="40" t="inlineStr">
+      <c r="B5" s="38" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
@@ -13094,45 +12994,45 @@
         <v>5</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="11" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr"/>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="13" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr"/>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="11" t="n">
+      <c r="F6" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="16" t="n">
-        <v>1</v>
+      <c r="G6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
@@ -13157,12 +13057,12 @@
       <c r="G7" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="H7" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="n">
+      <c r="A8" s="32" t="n">
         <v>0</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -13174,45 +13074,45 @@
         <v>67</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>53</v>
-      </c>
-      <c r="H8" s="16" t="n">
-        <v>0.7857142857142857</v>
+        <v>0</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0.582089552238806</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr"/>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="D9" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="11" t="n">
-        <v>53</v>
+      <c r="D9" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.5</v>
+        <v>0.5272727272727272</v>
       </c>
     </row>
     <row r="10">
@@ -13245,7 +13145,7 @@
       <c r="A11" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="40" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
@@ -13265,33 +13165,33 @@
       <c r="G11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="H11" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr"/>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C12" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="11" t="n">
+      <c r="E12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="13" t="n">
+      <c r="G12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13320,49 +13220,49 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="25" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Def Tier</t>
         </is>
       </c>
-      <c r="B1" s="25" t="inlineStr">
+      <c r="B1" s="24" t="inlineStr">
         <is>
           <t>Direction</t>
         </is>
       </c>
-      <c r="C1" s="25" t="inlineStr">
+      <c r="C1" s="24" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="D1" s="25" t="inlineStr">
+      <c r="D1" s="24" t="inlineStr">
         <is>
           <t>Decided</t>
         </is>
       </c>
-      <c r="E1" s="25" t="inlineStr">
+      <c r="E1" s="24" t="inlineStr">
         <is>
           <t>Hits</t>
         </is>
       </c>
-      <c r="F1" s="25" t="inlineStr">
+      <c r="F1" s="24" t="inlineStr">
         <is>
           <t>Misses</t>
         </is>
       </c>
-      <c r="G1" s="25" t="inlineStr">
+      <c r="G1" s="24" t="inlineStr">
         <is>
           <t>Voids</t>
         </is>
       </c>
-      <c r="H1" s="25" t="inlineStr">
+      <c r="H1" s="24" t="inlineStr">
         <is>
           <t>Hit Rate</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="34" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>weak</t>
         </is>
@@ -13376,45 +13276,45 @@
         <v>16</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F2" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="11" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr"/>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="D3" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="E3" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="G2" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="H2" s="13" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr"/>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="D3" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="E3" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G3" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="H3" s="13" t="n">
-        <v>0.2857142857142857</v>
+      <c r="F3" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="G3" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="11" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="4">
@@ -13439,7 +13339,7 @@
       <c r="G4" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="13" t="n">
+      <c r="H4" s="11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13449,7 +13349,7 @@
           <t>good</t>
         </is>
       </c>
-      <c r="B5" s="40" t="inlineStr">
+      <c r="B5" s="38" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
@@ -13458,45 +13358,45 @@
         <v>47</v>
       </c>
       <c r="D5" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="E5" s="4" t="n">
-        <v>10</v>
-      </c>
       <c r="F5" s="4" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
+      </c>
+      <c r="H5" s="11" t="n">
+        <v>0.425531914893617</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr"/>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr"/>
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="D6" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>27</v>
-      </c>
-      <c r="H6" s="13" t="n">
-        <v>0.3636363636363636</v>
+      <c r="D6" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="11" t="n">
+        <v>0.3684210526315789</v>
       </c>
     </row>
     <row r="7">
@@ -13526,7 +13426,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>elite</t>
         </is>
@@ -13540,45 +13440,45 @@
         <v>54</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H8" s="16" t="n">
-        <v>0.76</v>
+        <v>0.6851851851851852</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr"/>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="D9" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" s="11" t="n">
-        <v>29</v>
-      </c>
-      <c r="H9" s="16" t="n">
-        <v>0.75</v>
+      <c r="D9" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>0.6486486486486487</v>
       </c>
     </row>
     <row r="10">
@@ -13632,49 +13532,49 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="25" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Def Rank Bucket</t>
         </is>
       </c>
-      <c r="B1" s="25" t="inlineStr">
+      <c r="B1" s="24" t="inlineStr">
         <is>
           <t>Direction</t>
         </is>
       </c>
-      <c r="C1" s="25" t="inlineStr">
+      <c r="C1" s="24" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="D1" s="25" t="inlineStr">
+      <c r="D1" s="24" t="inlineStr">
         <is>
           <t>Decided</t>
         </is>
       </c>
-      <c r="E1" s="25" t="inlineStr">
+      <c r="E1" s="24" t="inlineStr">
         <is>
           <t>Hits</t>
         </is>
       </c>
-      <c r="F1" s="25" t="inlineStr">
+      <c r="F1" s="24" t="inlineStr">
         <is>
           <t>Misses</t>
         </is>
       </c>
-      <c r="G1" s="25" t="inlineStr">
+      <c r="G1" s="24" t="inlineStr">
         <is>
           <t>Voids</t>
         </is>
       </c>
-      <c r="H1" s="25" t="inlineStr">
+      <c r="H1" s="24" t="inlineStr">
         <is>
           <t>Hit Rate</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="34" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>26-30</t>
         </is>
@@ -13688,45 +13588,45 @@
         <v>117</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>53</v>
+        <v>117</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="G2" s="10" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>0.5849056603773585</v>
+        <v>0.5384615384615384</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr"/>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr"/>
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n">
+      <c r="C3" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="D3" s="11" t="n">
-        <v>26</v>
-      </c>
-      <c r="E3" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="G3" s="11" t="n">
-        <v>64</v>
-      </c>
-      <c r="H3" s="13" t="n">
-        <v>0.4615384615384616</v>
+      <c r="D3" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="E3" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="F3" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="G3" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="11" t="n">
+        <v>0.4888888888888889</v>
       </c>
     </row>
     <row r="4">
